--- a/audit-engine/tests/fixtures-sinteticos/mensais/posicao-2026-06.xlsx
+++ b/audit-engine/tests/fixtures-sinteticos/mensais/posicao-2026-06.xlsx
@@ -501,10 +501,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>470000</v>
+        <v>530000</v>
       </c>
       <c r="D5">
-        <v>470000</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -615,10 +615,10 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>470000</v>
+        <v>530000</v>
       </c>
       <c r="D14">
-        <v>470000</v>
+        <v>530000</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -629,10 +629,10 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>20000</v>
+        <v>80000</v>
       </c>
       <c r="D15">
-        <v>20000</v>
+        <v>80000</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -640,10 +640,10 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>1080000</v>
+        <v>1140000</v>
       </c>
       <c r="D16">
-        <v>1080000</v>
+        <v>1140000</v>
       </c>
     </row>
   </sheetData>

--- a/audit-engine/tests/fixtures-sinteticos/mensais/posicao-2026-06.xlsx
+++ b/audit-engine/tests/fixtures-sinteticos/mensais/posicao-2026-06.xlsx
@@ -868,10 +868,10 @@
         <v>8</v>
       </c>
       <c r="C8">
-        <v>256000</v>
+        <v>216000</v>
       </c>
       <c r="D8">
-        <v>256000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -882,10 +882,10 @@
         <v>4</v>
       </c>
       <c r="C9">
-        <v>256000</v>
+        <v>216000</v>
       </c>
       <c r="D9">
-        <v>256000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -893,10 +893,10 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>640000</v>
+        <v>600000</v>
       </c>
       <c r="D10">
-        <v>640000</v>
+        <v>600000</v>
       </c>
     </row>
   </sheetData>
